--- a/data/consolidated/The_Melting_Pod_Analytics_Consolidated.xlsx
+++ b/data/consolidated/The_Melting_Pod_Analytics_Consolidated.xlsx
@@ -10046,124 +10046,124 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="42" t="inlineStr">
         <is>
           <t>S1 E2</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="42" t="inlineStr">
         <is>
           <t>Biden and the Border (Part 1), with Charanya Krishnaswami</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="42" t="inlineStr">
         <is>
           <t>Feb 22, 2026</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="42" t="inlineStr">
         <is>
           <t>1 hr 13 min</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="42" t="n">
         <v>194</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="42" t="n">
         <v>149</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" s="42" t="n">
         <v>1497</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17" s="42" t="n">
         <v>0.78</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="42" t="inlineStr">
         <is>
           <t>S1 E1</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="42" t="inlineStr">
         <is>
           <t>Welcome to The Melting Pod</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="42" t="inlineStr">
         <is>
           <t>Feb 22, 2026</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="42" t="inlineStr">
         <is>
           <t>52 min</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="42" t="n">
         <v>243</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="42" t="n">
         <v>149</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" s="42" t="n">
         <v>1244</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18" s="42" t="n">
         <v>0.64</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="42" t="inlineStr">
         <is>
           <t>Episode NaN</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="42" t="inlineStr">
         <is>
           <t>Trailer: What is The Melting Pod?</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="42" t="inlineStr">
         <is>
           <t>Feb 22, 2026</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="42" t="inlineStr">
         <is>
           <t>2 min</t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="42" t="n">
         <v>74</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" s="42" t="n">
         <v>65</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" s="42" t="n">
         <v>95</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19" s="42" t="n">
         <v>0.9</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="42" t="inlineStr">
         <is>
           <t>Sum of listed episodes</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="42" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="42" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="G20">
+      <c r="G20" s="42">
         <f>SUM(G5:G19)</f>
         <v/>
       </c>
@@ -10183,7 +10183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B48"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="42" min="1" max="1"/>
@@ -10200,7 +10200,7 @@
     <row r="2" ht="15" customHeight="1" s="43">
       <c r="A2" s="75" t="inlineStr">
         <is>
-          <t>List as shown; screenshot is truncated at the bottom (smallest visible = 5). Listed cities therefore do not sum to the 671 'All Cities' total. Per-city breakdown below is from the original Feb–Jul 2026 export and has not been refreshed with the Sep 2026 update — only the 'All Cities' total and the top 5 (Washington D.C., Baltimore, Seattle, New York City, Los Angeles) are current as of Sep 2026.</t>
+          <t>Full list from the Sep 2026 "See All" cities view. Listed cities sum to 840, which EXCEEDS the 671 "All Cities" total — consistent with Apple's own methodology ("Listeners" are unique devices, not additive), evidently extended across cities too: the same listener can be counted in more than one city. Not a truncation artifact this time.</t>
         </is>
       </c>
     </row>
@@ -10269,21 +10269,21 @@
     <row r="10" ht="15" customHeight="1" s="43">
       <c r="A10" s="71" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="B10" s="50" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="43">
       <c r="A11" s="71" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="B11" s="50" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="43">
@@ -10293,37 +10293,37 @@
         </is>
       </c>
       <c r="B12" s="50" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="43">
       <c r="A13" s="71" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>San Jose</t>
         </is>
       </c>
       <c r="B13" s="50" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="43">
       <c r="A14" s="71" t="inlineStr">
         <is>
-          <t>San Jose</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="B14" s="50" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="43">
       <c r="A15" s="71" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Wilmington</t>
         </is>
       </c>
       <c r="B15" s="50" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="43">
@@ -10333,127 +10333,127 @@
         </is>
       </c>
       <c r="B16" s="50" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="43">
       <c r="A17" s="71" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="B17" s="50" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="43">
       <c r="A18" s="71" t="inlineStr">
         <is>
-          <t>Wilmington</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="B18" s="50" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="43">
       <c r="A19" s="71" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="B19" s="50" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="43">
       <c r="A20" s="71" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="B20" s="50" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="43">
       <c r="A21" s="71" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="B21" s="50" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="43">
       <c r="A22" s="71" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="B22" s="50" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="43">
       <c r="A23" s="71" t="inlineStr">
         <is>
-          <t>Hartford</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="B23" s="50" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="43">
       <c r="A24" s="71" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>London</t>
         </is>
       </c>
       <c r="B24" s="50" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="43">
       <c r="A25" s="71" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Hartford</t>
         </is>
       </c>
       <c r="B25" s="50" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="43">
       <c r="A26" s="71" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="B26" s="50" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="43">
       <c r="A27" s="71" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Worcester</t>
         </is>
       </c>
       <c r="B27" s="50" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="43">
       <c r="A28" s="71" t="inlineStr">
         <is>
-          <t>Worcester</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="B28" s="50" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="43">
@@ -10463,7 +10463,7 @@
         </is>
       </c>
       <c r="B29" s="50" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="43">
@@ -10473,123 +10473,183 @@
         </is>
       </c>
       <c r="B30" s="50" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="43">
       <c r="A31" s="71" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="B31" s="50" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="43">
       <c r="A32" s="71" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Leesburg</t>
         </is>
       </c>
       <c r="B32" s="50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="43">
       <c r="A33" s="71" t="inlineStr">
         <is>
-          <t>Oakland</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="B33" s="50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="43">
       <c r="A34" s="71" t="inlineStr">
         <is>
-          <t>Las Vegas</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="B34" s="50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="43">
       <c r="A35" s="71" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>Oakland</t>
         </is>
       </c>
       <c r="B35" s="50" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="43">
       <c r="A36" s="71" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Las Vegas</t>
         </is>
       </c>
       <c r="B36" s="50" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="43">
       <c r="A37" s="71" t="inlineStr">
         <is>
-          <t>Leesburg</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="B37" s="50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="43">
       <c r="A38" s="71" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Anaheim</t>
         </is>
       </c>
       <c r="B38" s="50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="43">
       <c r="A39" s="71" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Concord</t>
         </is>
       </c>
       <c r="B39" s="50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="43">
       <c r="A40" s="71" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="B40" s="50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="43">
       <c r="A41" s="71" t="inlineStr">
         <is>
-          <t>Anaheim</t>
+          <t>Bellingham</t>
         </is>
       </c>
       <c r="B41" s="50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="43">
       <c r="A42" s="75" t="inlineStr">
         <is>
-          <t>…list truncated in screenshot</t>
+          <t>Cincinnati</t>
+        </is>
+      </c>
+      <c r="B42" s="42" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="42" t="inlineStr">
+        <is>
+          <t>Columbus</t>
+        </is>
+      </c>
+      <c r="B43" s="42" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="42" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
+      <c r="B44" s="42" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="42" t="inlineStr">
+        <is>
+          <t>Pittsburgh</t>
+        </is>
+      </c>
+      <c r="B45" s="42" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="42" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="B46" s="42" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="42" t="inlineStr">
+        <is>
+          <t>Tacoma</t>
+        </is>
+      </c>
+      <c r="B47" s="42" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="42" t="inlineStr">
+        <is>
+          <t>listed cities sum to more than the total — Apple's 'Listeners' aren't additive across cities, same as across episodes</t>
         </is>
       </c>
     </row>

--- a/data/consolidated/The_Melting_Pod_Analytics_Consolidated.xlsx
+++ b/data/consolidated/The_Melting_Pod_Analytics_Consolidated.xlsx
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="B6" s="50" t="n">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="C6" s="50" t="n">
         <v>521</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="B7" s="50" t="n">
-        <v>1934</v>
+        <v>2250</v>
       </c>
       <c r="C7" s="50" t="n">
         <v>13600</v>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="F7" s="49" t="inlineStr">
         <is>
-          <t>Apple 'Plays' = "The total number of times people pressed play on your episode" (Apple). Spotify 'Plays' (standard effective 11 Jun 2026) counts an episode "watched or listened to for at least thirty seconds" (Spotify); header value is rounded. YouTube 'Views' = times a video was watched (unique + repeat). These are PLAY events; Megaphone counts DOWNLOADS instead, so the cross-platform residual sits on the next row, not here.</t>
+          <t>Apple 'Plays' = "The total number of times people pressed play on your episode" (Apple). Spotify 'Plays' (standard effective 11 Jun 2026) counts an episode "watched or listened to for at least thirty seconds" (Spotify); 2,250 is the exact sum of per-episode plays from Spotify's own "Plays since published" export (as of Sep 11, 2026), not a rounded header figure. YouTube 'Views' = times a video was watched (unique + repeat). These are PLAY events; Megaphone counts DOWNLOADS instead, so the cross-platform residual sits on the next row, not here.</t>
         </is>
       </c>
     </row>
@@ -10046,124 +10046,124 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="42" t="inlineStr">
         <is>
           <t>S1 E2</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="42" t="inlineStr">
         <is>
           <t>Biden and the Border (Part 1), with Charanya Krishnaswami</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="42" t="inlineStr">
         <is>
           <t>Feb 22, 2026</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="42" t="inlineStr">
         <is>
           <t>1 hr 13 min</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="42" t="n">
         <v>194</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="42" t="n">
         <v>149</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" s="42" t="n">
         <v>1497</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17" s="42" t="n">
         <v>0.78</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="42" t="inlineStr">
         <is>
           <t>S1 E1</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="42" t="inlineStr">
         <is>
           <t>Welcome to The Melting Pod</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="42" t="inlineStr">
         <is>
           <t>Feb 22, 2026</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="42" t="inlineStr">
         <is>
           <t>52 min</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="42" t="n">
         <v>243</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="42" t="n">
         <v>149</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" s="42" t="n">
         <v>1244</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18" s="42" t="n">
         <v>0.64</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="42" t="inlineStr">
         <is>
           <t>Episode NaN</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="42" t="inlineStr">
         <is>
           <t>Trailer: What is The Melting Pod?</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="42" t="inlineStr">
         <is>
           <t>Feb 22, 2026</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="42" t="inlineStr">
         <is>
           <t>2 min</t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="42" t="n">
         <v>74</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" s="42" t="n">
         <v>65</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" s="42" t="n">
         <v>95</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19" s="42" t="n">
         <v>0.9</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="42" t="inlineStr">
         <is>
           <t>Sum of listed episodes</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="42" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="42" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="G20">
+      <c r="G20" s="42">
         <f>SUM(G5:G19)</f>
         <v/>
       </c>

--- a/data/consolidated/The_Melting_Pod_Analytics_Consolidated.xlsx
+++ b/data/consolidated/The_Melting_Pod_Analytics_Consolidated.xlsx
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="E6" s="50" t="n">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="F6" s="49" t="inlineStr">
         <is>
-          <t>Apple 'Followers' = "The total number of people following your show" (Apple Podcasts Connect). Spotify 'Followers' = listeners who tapped Follow. YouTube 'Subscribers' shown here is the NET change for the period (gained minus lost); the overview reads "+178". Opt-in audience, not play volume.</t>
+          <t>Apple 'Followers' = "The total number of people following your show" (Apple Podcasts Connect). Spotify 'Followers' = listeners who tapped Follow. YouTube 'Subscribers' shown here is the NET change since channel start (cumulative subscriber-count series through Sep 10, 2026 reads 194); Opt-in audience, not play volume.</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="E7" s="50" t="n">
-        <v>7543</v>
+        <v>7888</v>
       </c>
       <c r="F7" s="49" t="inlineStr">
         <is>
@@ -1162,11 +1162,11 @@
         </is>
       </c>
       <c r="E11" s="53" t="n">
-        <v>241.5</v>
+        <v>312.6892</v>
       </c>
       <c r="F11" s="49" t="inlineStr">
         <is>
-          <t>Apple 'Time Listened' = cumulative hours listened across all listeners and followers (Apple); header "1.7K" = Following ~1,306 + Not-following 394 ≈ 1,700 (Following is Apple's own rounded "1.3K" display, not an exact figure this time). YouTube 'Watch time' = total hours viewers spent watching, including complete and partial views.</t>
+          <t>Apple 'Time Listened' = cumulative hours listened across all listeners and followers (Apple); header "1.7K" = Following ~1,306 + Not-following 394 ≈ 1,700 (Following is Apple's own rounded "1.3K" display, not an exact figure this time). YouTube 'Watch time' = total hours viewers spent watching, including complete and partial views; 312.6892 h from the fresh Traffic Sources export (through ~Sep 2026), combining video + Shorts.</t>
         </is>
       </c>
     </row>
@@ -1252,11 +1252,11 @@
         </is>
       </c>
       <c r="E14" s="50" t="n">
-        <v>17427</v>
+        <v>23526</v>
       </c>
       <c r="F14" s="49" t="inlineStr">
         <is>
-          <t>YouTube 'Impressions' = how often your video thumbnails were shown to viewers on YouTube (registered impressions). 'Impressions CTR' = the percentage of impressions that resulted in a viewer clicking your video and watching it (4.2%). 'Average view duration' = total watch time divided by total views (4:05).</t>
+          <t>YouTube 'Impressions' = how often your video thumbnails were shown to viewers on YouTube (registered impressions). 'Impressions CTR' = the percentage of impressions that resulted in a viewer clicking your video and watching it (3.72% as of the fresh Traffic Sources export). 'Average view duration' = total watch time divided by total views (4:52 as of the same export). The YouTube Funnel tab still reflects the older Jan 1-Jul 14 export and has not been refreshed to match.</t>
         </is>
       </c>
     </row>
@@ -1353,14 +1353,14 @@
     <row r="1" ht="15.75" customHeight="1" s="43">
       <c r="A1" s="74" t="inlineStr">
         <is>
-          <t>YouTube — Content (per video)  ·  Jan 1 – Jul 14, 2026</t>
+          <t>YouTube — Full episodes (per video)  ·  All-time (fresh export, ~through Sep 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="43">
       <c r="A2" s="75" t="inlineStr">
         <is>
-          <t>Durations read from thumbnail overlays. '%' columns are each row's share of the channel total.</t>
+          <t>Long-form episode videos only — Shorts excluded (no fresh per-Short breakdown was exported this round; the prior Jan 1-Jul 14 tab mixed Shorts into this list, this one does not). No per-video Subscribers figure in this export, so those columns are dropped rather than shown as unavailable placeholders. One entry ('Three Big Lies About Immigrants and Fraud...') appears twice in the source export — a duplicate/near-duplicate video ID with a single view — kept as reported rather than silently merged or dropped.</t>
         </is>
       </c>
     </row>
@@ -1397,762 +1397,588 @@
       </c>
       <c r="G4" s="46" t="inlineStr">
         <is>
-          <t>Subscribers</t>
+          <t>Impressions</t>
         </is>
       </c>
       <c r="H4" s="46" t="inlineStr">
         <is>
-          <t>Subscribers %</t>
-        </is>
-      </c>
-      <c r="I4" s="46" t="inlineStr">
-        <is>
-          <t>Impressions</t>
-        </is>
-      </c>
-      <c r="J4" s="46" t="inlineStr">
-        <is>
           <t>Impr. CTR</t>
         </is>
       </c>
+      <c r="I4" s="46" t="n"/>
+      <c r="J4" s="46" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="43">
       <c r="A5" s="71" t="inlineStr">
         <is>
-          <t>There's No Differentiation Among U.S. Citizens</t>
+          <t>Welcome to The Melting Pod</t>
         </is>
       </c>
       <c r="B5" s="48" t="inlineStr">
         <is>
-          <t>0:22</t>
+          <t>52:22</t>
         </is>
       </c>
       <c r="C5" s="50" t="n">
-        <v>1462</v>
+        <v>256</v>
       </c>
       <c r="D5" s="79" t="n">
-        <v>0.194</v>
+        <v>0.1819</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>1.5</v>
+        <v>34.665</v>
       </c>
       <c r="F5" s="79" t="n">
-        <v>0.006</v>
+        <v>0.1208</v>
       </c>
       <c r="G5" s="50" t="n">
-        <v>2</v>
+        <v>2603</v>
       </c>
       <c r="H5" s="79" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="I5" s="50" t="n">
-        <v>367</v>
-      </c>
-      <c r="J5" s="79" t="n">
-        <v>0.035</v>
-      </c>
+        <v>0.0634</v>
+      </c>
+      <c r="I5" s="50" t="n"/>
+      <c r="J5" s="79" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1" s="43">
       <c r="A6" s="71" t="inlineStr">
         <is>
-          <t>Never Mind Kristi Noem; Nothing Changes While S…</t>
+          <t>The Heartbreak of Immigration Reform, with Esther Olavarria</t>
         </is>
       </c>
       <c r="B6" s="48" t="inlineStr">
         <is>
-          <t>1:28</t>
+          <t>1:38:21</t>
         </is>
       </c>
       <c r="C6" s="50" t="n">
-        <v>1395</v>
+        <v>165</v>
       </c>
       <c r="D6" s="79" t="n">
-        <v>0.185</v>
+        <v>0.1173</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>7.6</v>
+        <v>47.6568</v>
       </c>
       <c r="F6" s="79" t="n">
-        <v>0.032</v>
+        <v>0.1661</v>
       </c>
       <c r="G6" s="50" t="n">
-        <v>4</v>
+        <v>1440</v>
       </c>
       <c r="H6" s="79" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="I6" s="50" t="n">
-        <v>410</v>
-      </c>
-      <c r="J6" s="79" t="n">
-        <v>0.046</v>
-      </c>
+        <v>0.0625</v>
+      </c>
+      <c r="I6" s="50" t="n"/>
+      <c r="J6" s="79" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1" s="43">
       <c r="A7" s="71" t="inlineStr">
         <is>
-          <t>All Good Immigration Policy Is Not A Pull Factor</t>
+          <t>Who's Afraid of the H-1B?</t>
         </is>
       </c>
       <c r="B7" s="48" t="inlineStr">
         <is>
-          <t>0:16</t>
+          <t>1:13:39</t>
         </is>
       </c>
       <c r="C7" s="50" t="n">
-        <v>1003</v>
+        <v>155</v>
       </c>
       <c r="D7" s="79" t="n">
-        <v>0.133</v>
+        <v>0.1102</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>0.9</v>
+        <v>42.5651</v>
       </c>
       <c r="F7" s="79" t="n">
-        <v>0.004</v>
+        <v>0.1483</v>
       </c>
       <c r="G7" s="50" t="n">
-        <v>0</v>
+        <v>1217</v>
       </c>
       <c r="H7" s="79" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="50" t="n">
-        <v>275</v>
-      </c>
-      <c r="J7" s="79" t="n">
-        <v>0.033</v>
-      </c>
+        <v>0.0772</v>
+      </c>
+      <c r="I7" s="50" t="n"/>
+      <c r="J7" s="79" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1" s="43">
       <c r="A8" s="71" t="inlineStr">
         <is>
-          <t>No, Elon Musk Won't "Go to War" to Save H-1B Visas</t>
+          <t>The Reality-Based Economics of Immigration, with Jenny Hunt</t>
         </is>
       </c>
       <c r="B8" s="48" t="inlineStr">
         <is>
-          <t>0:52</t>
+          <t>48:40</t>
         </is>
       </c>
       <c r="C8" s="50" t="n">
-        <v>906</v>
+        <v>125</v>
       </c>
       <c r="D8" s="79" t="n">
-        <v>0.12</v>
+        <v>0.0888</v>
       </c>
       <c r="E8" s="53" t="n">
-        <v>4.3</v>
+        <v>11.8214</v>
       </c>
       <c r="F8" s="79" t="n">
-        <v>0.018</v>
+        <v>0.0412</v>
       </c>
       <c r="G8" s="50" t="n">
-        <v>1</v>
+        <v>4446</v>
       </c>
       <c r="H8" s="79" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="I8" s="50" t="n">
-        <v>201</v>
-      </c>
-      <c r="J8" s="79" t="n">
-        <v>0.04</v>
-      </c>
+        <v>0.0166</v>
+      </c>
+      <c r="I8" s="50" t="n"/>
+      <c r="J8" s="79" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1" s="43">
       <c r="A9" s="71" t="inlineStr">
         <is>
-          <t>Pundits Erroneously Blaming "Woke" Staffers for B…</t>
+          <t>Confessions of an Immigration Bureaucrat, with Michael Valverde</t>
         </is>
       </c>
       <c r="B9" s="48" t="inlineStr">
         <is>
-          <t>2:55</t>
+          <t>1:05:07</t>
         </is>
       </c>
       <c r="C9" s="50" t="n">
-        <v>858</v>
+        <v>123</v>
       </c>
       <c r="D9" s="79" t="n">
-        <v>0.114</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>9.699999999999999</v>
+        <v>33.7258</v>
       </c>
       <c r="F9" s="79" t="n">
-        <v>0.04</v>
+        <v>0.1175</v>
       </c>
       <c r="G9" s="50" t="n">
-        <v>1</v>
+        <v>3703</v>
       </c>
       <c r="H9" s="79" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="I9" s="50" t="n">
-        <v>120</v>
-      </c>
-      <c r="J9" s="79" t="n">
-        <v>0.042</v>
-      </c>
+        <v>0.0165</v>
+      </c>
+      <c r="I9" s="50" t="n"/>
+      <c r="J9" s="79" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1" s="43">
       <c r="A10" s="71" t="inlineStr">
         <is>
-          <t>DACA Day was Joyous #immigration #DACA</t>
+          <t>The Truth About ICE, with Jason Houser</t>
         </is>
       </c>
       <c r="B10" s="48" t="inlineStr">
         <is>
-          <t>1:01</t>
+          <t>1:01:43</t>
         </is>
       </c>
       <c r="C10" s="50" t="n">
-        <v>399</v>
+        <v>107</v>
       </c>
       <c r="D10" s="79" t="n">
-        <v>0.053</v>
+        <v>0.076</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>0.8</v>
+        <v>20.6923</v>
       </c>
       <c r="F10" s="79" t="n">
-        <v>0.003</v>
+        <v>0.0721</v>
       </c>
       <c r="G10" s="50" t="n">
-        <v>0</v>
+        <v>1706</v>
       </c>
       <c r="H10" s="79" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="50" t="n">
-        <v>158</v>
-      </c>
-      <c r="J10" s="79" t="n">
-        <v>0.044</v>
-      </c>
+        <v>0.0381</v>
+      </c>
+      <c r="I10" s="50" t="n"/>
+      <c r="J10" s="79" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1" s="43">
       <c r="A11" s="71" t="inlineStr">
         <is>
-          <t>Welcome to The Melting Pod</t>
+          <t>Biden and the Border (Part 1), with Charanya Krishnaswami</t>
         </is>
       </c>
       <c r="B11" s="48" t="inlineStr">
         <is>
-          <t>1:52:22</t>
+          <t>1:12:56</t>
         </is>
       </c>
       <c r="C11" s="50" t="n">
-        <v>236</v>
+        <v>97</v>
       </c>
       <c r="D11" s="79" t="n">
-        <v>0.031</v>
+        <v>0.0689</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>30.7</v>
+        <v>24.8097</v>
       </c>
       <c r="F11" s="79" t="n">
-        <v>0.127</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="G11" s="50" t="n">
-        <v>23</v>
+        <v>924</v>
       </c>
       <c r="H11" s="79" t="n">
-        <v>0.129</v>
-      </c>
-      <c r="I11" s="50" t="n">
-        <v>2471</v>
-      </c>
-      <c r="J11" s="79" t="n">
-        <v>0.063</v>
-      </c>
+        <v>0.0487</v>
+      </c>
+      <c r="I11" s="50" t="n"/>
+      <c r="J11" s="79" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" s="43">
       <c r="A12" s="71" t="inlineStr">
         <is>
-          <t>Jason Houser discussed the role of ICE officers.</t>
+          <t>News Digest: Green Card Chaos, Hunger Strikes, and Stern Dad Energy</t>
         </is>
       </c>
       <c r="B12" s="48" t="inlineStr">
         <is>
-          <t>0:34</t>
+          <t>1:08:08</t>
         </is>
       </c>
       <c r="C12" s="50" t="n">
-        <v>221</v>
+        <v>79</v>
       </c>
       <c r="D12" s="79" t="n">
-        <v>0.029</v>
+        <v>0.0561</v>
       </c>
       <c r="E12" s="53" t="n">
-        <v>0.3</v>
+        <v>16.1595</v>
       </c>
       <c r="F12" s="79" t="n">
-        <v>0.001</v>
+        <v>0.0563</v>
       </c>
       <c r="G12" s="50" t="n">
-        <v>1</v>
+        <v>1366</v>
       </c>
       <c r="H12" s="79" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="I12" s="50" t="n">
-        <v>120</v>
-      </c>
-      <c r="J12" s="79" t="n">
-        <v>0.083</v>
-      </c>
+        <v>0.0337</v>
+      </c>
+      <c r="I12" s="50" t="n"/>
+      <c r="J12" s="79" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="43">
       <c r="A13" s="71" t="inlineStr">
         <is>
-          <t>The Heartbreak of Immigration Reform, with Esthe…</t>
+          <t>Biden and the Border (Part 2), with Charanya Krishnaswami</t>
         </is>
       </c>
       <c r="B13" s="48" t="inlineStr">
         <is>
-          <t>1:38:21</t>
+          <t>1:09:03</t>
         </is>
       </c>
       <c r="C13" s="50" t="n">
-        <v>151</v>
+        <v>63</v>
       </c>
       <c r="D13" s="79" t="n">
-        <v>0.02</v>
+        <v>0.0448</v>
       </c>
       <c r="E13" s="53" t="n">
-        <v>45.6</v>
+        <v>16.6547</v>
       </c>
       <c r="F13" s="79" t="n">
-        <v>0.189</v>
+        <v>0.058</v>
       </c>
       <c r="G13" s="50" t="n">
-        <v>3</v>
+        <v>776</v>
       </c>
       <c r="H13" s="79" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="I13" s="50" t="n">
-        <v>1331</v>
-      </c>
-      <c r="J13" s="79" t="n">
-        <v>0.063</v>
-      </c>
+        <v>0.0425</v>
+      </c>
+      <c r="I13" s="50" t="n"/>
+      <c r="J13" s="79" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1" s="43">
       <c r="A14" s="71" t="inlineStr">
         <is>
-          <t>Who's Afraid of the H-1B?</t>
+          <t>Three Big Lies About Immigrants and Fraud, with Sonya Schwartz</t>
         </is>
       </c>
       <c r="B14" s="48" t="inlineStr">
         <is>
-          <t>1:13:39</t>
+          <t>56:20</t>
         </is>
       </c>
       <c r="C14" s="50" t="n">
-        <v>150</v>
+        <v>62</v>
       </c>
       <c r="D14" s="79" t="n">
-        <v>0.02</v>
+        <v>0.0441</v>
       </c>
       <c r="E14" s="53" t="n">
-        <v>40</v>
+        <v>10.0861</v>
       </c>
       <c r="F14" s="79" t="n">
-        <v>0.166</v>
+        <v>0.0351</v>
       </c>
       <c r="G14" s="50" t="n">
-        <v>7</v>
+        <v>570</v>
       </c>
       <c r="H14" s="79" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="I14" s="50" t="n">
-        <v>1158</v>
-      </c>
-      <c r="J14" s="79" t="n">
-        <v>0.079</v>
-      </c>
+        <v>0.0456</v>
+      </c>
+      <c r="I14" s="50" t="n"/>
+      <c r="J14" s="79" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1" s="43">
       <c r="A15" s="71" t="inlineStr">
         <is>
-          <t>We Must Offer an Affirmative Vision</t>
+          <t>DACA and the Dreamer Movement, with Felicia Escobar Carrillo</t>
         </is>
       </c>
       <c r="B15" s="48" t="inlineStr">
         <is>
-          <t>0:13</t>
+          <t>1:35:57</t>
         </is>
       </c>
       <c r="C15" s="50" t="n">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="D15" s="79" t="n">
-        <v>0.016</v>
+        <v>0.0355</v>
       </c>
       <c r="E15" s="53" t="n">
-        <v>0.1</v>
+        <v>14.3531</v>
       </c>
       <c r="F15" s="79" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="G15" s="50" t="n">
-        <v>0</v>
+        <v>1030</v>
       </c>
       <c r="H15" s="79" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="50" t="n">
-        <v>345</v>
-      </c>
-      <c r="J15" s="79" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.0311</v>
+      </c>
+      <c r="I15" s="50" t="n"/>
+      <c r="J15" s="79" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1" s="43">
       <c r="A16" s="71" t="inlineStr">
         <is>
-          <t>The Reality-Based Economics of Immigration, with …</t>
+          <t>Asylum Is Not a Loophole, with Colleen Zengotitabengoa</t>
         </is>
       </c>
       <c r="B16" s="48" t="inlineStr">
         <is>
-          <t>1:48:40</t>
+          <t>1:17:29</t>
         </is>
       </c>
       <c r="C16" s="50" t="n">
-        <v>118</v>
+        <v>49</v>
       </c>
       <c r="D16" s="79" t="n">
-        <v>0.016</v>
+        <v>0.0348</v>
       </c>
       <c r="E16" s="53" t="n">
-        <v>11.8</v>
+        <v>5.6282</v>
       </c>
       <c r="F16" s="79" t="n">
-        <v>0.049</v>
+        <v>0.0196</v>
       </c>
       <c r="G16" s="50" t="n">
-        <v>3</v>
+        <v>341</v>
       </c>
       <c r="H16" s="79" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="I16" s="50" t="n">
-        <v>4308</v>
-      </c>
-      <c r="J16" s="79" t="n">
-        <v>0.017</v>
-      </c>
+        <v>0.0411</v>
+      </c>
+      <c r="I16" s="50" t="n"/>
+      <c r="J16" s="79" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1" s="43">
       <c r="A17" s="71" t="inlineStr">
         <is>
-          <t>The Truth About ICE, with Jason Houser</t>
+          <t>News Dive: The Great De-Legalization, H-1B Follies, and Midterm Predictions</t>
         </is>
       </c>
       <c r="B17" s="48" t="inlineStr">
         <is>
-          <t>1:01:43</t>
+          <t>1:01:03</t>
         </is>
       </c>
       <c r="C17" s="50" t="n">
-        <v>102</v>
+        <v>27</v>
       </c>
       <c r="D17" s="79" t="n">
-        <v>0.014</v>
+        <v>0.0192</v>
       </c>
       <c r="E17" s="53" t="n">
-        <v>18.1</v>
+        <v>0.971</v>
       </c>
       <c r="F17" s="79" t="n">
-        <v>0.075</v>
+        <v>0.0034</v>
       </c>
       <c r="G17" s="50" t="n">
-        <v>3</v>
+        <v>197</v>
       </c>
       <c r="H17" s="79" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="I17" s="50" t="n">
-        <v>1594</v>
-      </c>
-      <c r="J17" s="79" t="n">
-        <v>0.039</v>
-      </c>
+        <v>0.0406</v>
+      </c>
+      <c r="I17" s="50" t="n"/>
+      <c r="J17" s="79" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1" s="43">
       <c r="A18" s="71" t="inlineStr">
         <is>
-          <t>Trailer: What is The Melting Pod?</t>
+          <t>A Winning Message on Immigration, with Beatriz Lopez</t>
         </is>
       </c>
       <c r="B18" s="48" t="inlineStr">
         <is>
-          <t>2:22</t>
+          <t>1:02:47</t>
         </is>
       </c>
       <c r="C18" s="50" t="n">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="D18" s="79" t="n">
-        <v>0.013</v>
+        <v>0.0171</v>
       </c>
       <c r="E18" s="53" t="n">
-        <v>0.5</v>
+        <v>6.8669</v>
       </c>
       <c r="F18" s="79" t="n">
-        <v>0.002</v>
+        <v>0.0239</v>
       </c>
       <c r="G18" s="50" t="n">
-        <v>9</v>
+        <v>274</v>
       </c>
       <c r="H18" s="79" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="I18" s="50" t="n">
-        <v>550</v>
-      </c>
-      <c r="J18" s="79" t="n">
-        <v>0.047</v>
-      </c>
+        <v>0.0438</v>
+      </c>
+      <c r="I18" s="50" t="n"/>
+      <c r="J18" s="79" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1" s="43">
       <c r="A19" s="71" t="inlineStr">
         <is>
-          <t>Biden and the Border (Part 1), with Charanya Krish…</t>
+          <t>Three Big Lies About Immigrants and Fraud, with Sonya Schwartz</t>
         </is>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>1:12:56</t>
+          <t>57:47</t>
         </is>
       </c>
       <c r="C19" s="50" t="n">
-        <v>85</v>
+        <v>1</v>
       </c>
       <c r="D19" s="79" t="n">
-        <v>0.011</v>
+        <v>0.0007</v>
       </c>
       <c r="E19" s="53" t="n">
-        <v>21.3</v>
+        <v>0.0025</v>
       </c>
       <c r="F19" s="79" t="n">
-        <v>0.08799999999999999</v>
+        <v>0</v>
       </c>
       <c r="G19" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="79" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="50" t="n">
-        <v>814</v>
-      </c>
-      <c r="J19" s="79" t="n">
-        <v>0.048</v>
-      </c>
+      <c r="H19" s="79" t="n"/>
+      <c r="I19" s="50" t="n"/>
+      <c r="J19" s="79" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1" s="43">
       <c r="A20" s="71" t="inlineStr">
         <is>
-          <t>News Digest: Green Card Chaos, Hunger Strikes, a…</t>
-        </is>
-      </c>
-      <c r="B20" s="48" t="inlineStr">
-        <is>
-          <t>1:08:08</t>
-        </is>
-      </c>
+          <t>Sum of rows shown</t>
+        </is>
+      </c>
+      <c r="B20" s="48" t="n"/>
       <c r="C20" s="50" t="n">
-        <v>71</v>
-      </c>
-      <c r="D20" s="79" t="n">
-        <v>0.008999999999999999</v>
-      </c>
+        <v>1383</v>
+      </c>
+      <c r="D20" s="79" t="n"/>
       <c r="E20" s="53" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="F20" s="79" t="n">
-        <v>0.059</v>
-      </c>
+        <v>286.6581</v>
+      </c>
+      <c r="F20" s="79" t="n"/>
       <c r="G20" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="79" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="I20" s="50" t="n">
-        <v>1193</v>
-      </c>
-      <c r="J20" s="79" t="n">
-        <v>0.038</v>
-      </c>
+        <v>20593</v>
+      </c>
+      <c r="H20" s="79" t="n"/>
+      <c r="I20" s="50" t="n"/>
+      <c r="J20" s="79" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1" s="43">
       <c r="A21" s="71" t="inlineStr">
         <is>
-          <t>Biden and the Border (Part 2), with Charanya Krish…</t>
-        </is>
-      </c>
-      <c r="B21" s="48" t="inlineStr">
-        <is>
-          <t>1:09:03</t>
-        </is>
-      </c>
+          <t>Channel total (videos only, per YouTube)</t>
+        </is>
+      </c>
+      <c r="B21" s="48" t="n"/>
       <c r="C21" s="50" t="n">
-        <v>55</v>
-      </c>
-      <c r="D21" s="79" t="n">
-        <v>0.007</v>
-      </c>
+        <v>1407</v>
+      </c>
+      <c r="D21" s="79" t="n"/>
       <c r="E21" s="53" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="F21" s="79" t="n">
-        <v>0.062</v>
-      </c>
+        <v>286.9659</v>
+      </c>
+      <c r="F21" s="79" t="n"/>
       <c r="G21" s="50" t="n">
-        <v>1</v>
+        <v>20770</v>
       </c>
       <c r="H21" s="79" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="I21" s="50" t="n">
-        <v>735</v>
-      </c>
-      <c r="J21" s="79" t="n">
-        <v>0.042</v>
-      </c>
+        <v>0.0373</v>
+      </c>
+      <c r="I21" s="50" t="n"/>
+      <c r="J21" s="79" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1" s="43">
-      <c r="A22" s="71" t="inlineStr">
-        <is>
-          <t>DACA and the Dreamer Movement, with Felicia Esc…</t>
-        </is>
-      </c>
-      <c r="B22" s="48" t="inlineStr">
-        <is>
-          <t>1:35:57</t>
-        </is>
-      </c>
-      <c r="C22" s="50" t="n">
-        <v>50</v>
-      </c>
-      <c r="D22" s="79" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="E22" s="53" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="F22" s="79" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="G22" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="79" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="50" t="n">
-        <v>959</v>
-      </c>
-      <c r="J22" s="79" t="n">
-        <v>0.033</v>
-      </c>
+      <c r="A22" s="71" t="n"/>
+      <c r="B22" s="48" t="n"/>
+      <c r="C22" s="50" t="n"/>
+      <c r="D22" s="79" t="n"/>
+      <c r="E22" s="53" t="n"/>
+      <c r="F22" s="79" t="n"/>
+      <c r="G22" s="50" t="n"/>
+      <c r="H22" s="79" t="n"/>
+      <c r="I22" s="50" t="n"/>
+      <c r="J22" s="79" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1" s="43">
-      <c r="A23" s="71" t="inlineStr">
-        <is>
-          <t>A Winning Message on Immigration, with Beatriz L…</t>
-        </is>
-      </c>
-      <c r="B23" s="48" t="inlineStr">
-        <is>
-          <t>1:02:47</t>
-        </is>
-      </c>
-      <c r="C23" s="50" t="n">
-        <v>11</v>
-      </c>
-      <c r="D23" s="79" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="E23" s="53" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F23" s="79" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="G23" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="79" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="50" t="n">
-        <v>133</v>
-      </c>
-      <c r="J23" s="79" t="n">
-        <v>0.045</v>
-      </c>
+      <c r="A23" s="71" t="n"/>
+      <c r="B23" s="48" t="n"/>
+      <c r="C23" s="50" t="n"/>
+      <c r="D23" s="79" t="n"/>
+      <c r="E23" s="53" t="n"/>
+      <c r="F23" s="79" t="n"/>
+      <c r="G23" s="50" t="n"/>
+      <c r="H23" s="79" t="n"/>
+      <c r="I23" s="50" t="n"/>
+      <c r="J23" s="79" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1" s="43">
-      <c r="A24" s="76" t="inlineStr">
-        <is>
-          <t>Sum of rows shown</t>
-        </is>
-      </c>
+      <c r="A24" s="76" t="n"/>
       <c r="B24" s="77" t="n"/>
-      <c r="C24" s="64">
-        <f>SUM(C5:C23)</f>
-        <v/>
-      </c>
+      <c r="C24" s="64" t="n"/>
       <c r="D24" s="77" t="n"/>
-      <c r="E24" s="80">
-        <f>SUM(E5:E23)</f>
-        <v/>
-      </c>
+      <c r="E24" s="80" t="n"/>
       <c r="F24" s="77" t="n"/>
-      <c r="G24" s="64">
-        <f>SUM(G5:G23)</f>
-        <v/>
-      </c>
+      <c r="G24" s="64" t="n"/>
       <c r="H24" s="77" t="n"/>
-      <c r="I24" s="64">
-        <f>SUM(I5:I23)</f>
-        <v/>
-      </c>
+      <c r="I24" s="64" t="n"/>
       <c r="J24" s="77" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1" s="43">
-      <c r="A25" s="76" t="inlineStr">
-        <is>
-          <t>Channel total (per YouTube)</t>
-        </is>
-      </c>
+      <c r="A25" s="76" t="n"/>
       <c r="B25" s="77" t="n"/>
-      <c r="C25" s="64" t="n">
-        <v>7543</v>
-      </c>
+      <c r="C25" s="64" t="n"/>
       <c r="D25" s="77" t="n"/>
-      <c r="E25" s="80" t="n">
-        <v>241.5</v>
-      </c>
+      <c r="E25" s="80" t="n"/>
       <c r="F25" s="77" t="n"/>
-      <c r="G25" s="64" t="n">
-        <v>178</v>
-      </c>
+      <c r="G25" s="64" t="n"/>
       <c r="H25" s="77" t="n"/>
-      <c r="I25" s="64" t="n">
-        <v>17427</v>
-      </c>
-      <c r="J25" s="81" t="n">
-        <v>0.042</v>
-      </c>
+      <c r="I25" s="64" t="n"/>
+      <c r="J25" s="81" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:J25"/>
@@ -2184,14 +2010,14 @@
     <row r="1" ht="15.75" customHeight="1" s="43">
       <c r="A1" s="74" t="inlineStr">
         <is>
-          <t>YouTube — Traffic Sources  ·  Jan 1 – Jul 14, 2026</t>
+          <t>YouTube — Traffic Sources  ·  All-time (fresh export, ~through Sep 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="43">
       <c r="A2" s="75" t="inlineStr">
         <is>
-          <t>Blank Impressions/CTR cells shown as '—' in YouTube (not impression-served). '%' columns are share of channel Views / Watch time.</t>
+          <t>Blank Impressions/CTR cells shown as '—' in YouTube (not impression-served). '%' columns are share of channel Views / Watch time. Refreshed Sep 2026 — supersedes the prior Jan 1-Jul 14 snapshot.</t>
         </is>
       </c>
     </row>
@@ -2244,13 +2070,13 @@
         </is>
       </c>
       <c r="B5" s="64" t="n">
-        <v>17427</v>
+        <v>23526</v>
       </c>
       <c r="C5" s="81" t="n">
-        <v>0.042</v>
+        <v>0.0372</v>
       </c>
       <c r="D5" s="64" t="n">
-        <v>7543</v>
+        <v>7888</v>
       </c>
       <c r="E5" s="78" t="inlineStr">
         <is>
@@ -2259,11 +2085,11 @@
       </c>
       <c r="F5" s="78" t="inlineStr">
         <is>
-          <t>4:05</t>
+          <t>0:04:52</t>
         </is>
       </c>
       <c r="G5" s="80" t="n">
-        <v>241.5</v>
+        <v>312.6892</v>
       </c>
       <c r="H5" s="78" t="inlineStr">
         <is>
@@ -2274,35 +2100,31 @@
     <row r="6" ht="15" customHeight="1" s="43">
       <c r="A6" s="71" t="inlineStr">
         <is>
-          <t>Shorts feed</t>
-        </is>
-      </c>
-      <c r="B6" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C6" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Suggested videos</t>
+        </is>
+      </c>
+      <c r="B6" s="48" t="n">
+        <v>10636</v>
+      </c>
+      <c r="C6" s="48" t="n">
+        <v>0.007900000000000001</v>
       </c>
       <c r="D6" s="50" t="n">
-        <v>5952</v>
+        <v>147</v>
       </c>
       <c r="E6" s="79" t="n">
-        <v>0.789</v>
+        <v>0.0186</v>
       </c>
       <c r="F6" s="48" t="inlineStr">
         <is>
-          <t>0:35</t>
+          <t>0:15:56</t>
         </is>
       </c>
       <c r="G6" s="53" t="n">
-        <v>22.7</v>
+        <v>38.5386</v>
       </c>
       <c r="H6" s="79" t="n">
-        <v>0.094</v>
+        <v>0.1232</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="43">
@@ -2312,157 +2134,161 @@
         </is>
       </c>
       <c r="B7" s="50" t="n">
-        <v>3451</v>
+        <v>4239</v>
       </c>
       <c r="C7" s="79" t="n">
-        <v>0.09</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="D7" s="50" t="n">
-        <v>457</v>
+        <v>540</v>
       </c>
       <c r="E7" s="79" t="n">
-        <v>0.061</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="F7" s="48" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>0:15:38</t>
         </is>
       </c>
       <c r="G7" s="53" t="n">
-        <v>97</v>
+        <v>127.2212</v>
       </c>
       <c r="H7" s="79" t="n">
-        <v>0.402</v>
+        <v>0.4069</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="43">
       <c r="A8" s="71" t="inlineStr">
         <is>
-          <t>YouTube search</t>
+          <t>Browse features</t>
         </is>
       </c>
       <c r="B8" s="50" t="n">
-        <v>2066</v>
+        <v>4349</v>
       </c>
       <c r="C8" s="79" t="n">
-        <v>0.077</v>
+        <v>0.0437</v>
       </c>
       <c r="D8" s="50" t="n">
-        <v>250</v>
+        <v>305</v>
       </c>
       <c r="E8" s="79" t="n">
-        <v>0.033</v>
+        <v>0.0387</v>
       </c>
       <c r="F8" s="48" t="inlineStr">
         <is>
-          <t>3:28</t>
+          <t>0:11:11</t>
         </is>
       </c>
       <c r="G8" s="53" t="n">
-        <v>11.8</v>
+        <v>50.2126</v>
       </c>
       <c r="H8" s="79" t="n">
-        <v>0.049</v>
+        <v>0.1606</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="43">
       <c r="A9" s="71" t="inlineStr">
         <is>
-          <t>Other YouTube features</t>
-        </is>
-      </c>
-      <c r="B9" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C9" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Playlists</t>
+        </is>
+      </c>
+      <c r="B9" s="48" t="n">
+        <v>1561</v>
+      </c>
+      <c r="C9" s="48" t="n">
+        <v>0.025</v>
       </c>
       <c r="D9" s="50" t="n">
-        <v>229</v>
+        <v>94</v>
       </c>
       <c r="E9" s="79" t="n">
-        <v>0.03</v>
+        <v>0.0119</v>
       </c>
       <c r="F9" s="48" t="inlineStr">
         <is>
-          <t>5:14</t>
+          <t>0:10:10</t>
         </is>
       </c>
       <c r="G9" s="53" t="n">
-        <v>13.1</v>
+        <v>13.9138</v>
       </c>
       <c r="H9" s="79" t="n">
-        <v>0.054</v>
+        <v>0.0445</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="43">
       <c r="A10" s="71" t="inlineStr">
         <is>
-          <t>Browse features</t>
-        </is>
-      </c>
-      <c r="B10" s="50" t="n">
-        <v>3747</v>
-      </c>
-      <c r="C10" s="79" t="n">
-        <v>0.042</v>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="B10" s="50" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C10" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="D10" s="50" t="n">
-        <v>222</v>
+        <v>115</v>
       </c>
       <c r="E10" s="79" t="n">
-        <v>0.029</v>
+        <v>0.0146</v>
       </c>
       <c r="F10" s="48" t="inlineStr">
         <is>
-          <t>9:57</t>
+          <t>0:07:04</t>
         </is>
       </c>
       <c r="G10" s="53" t="n">
-        <v>35.7</v>
+        <v>12.0267</v>
       </c>
       <c r="H10" s="79" t="n">
-        <v>0.148</v>
+        <v>0.0385</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="43">
       <c r="A11" s="71" t="inlineStr">
         <is>
-          <t>Suggested videos</t>
-        </is>
-      </c>
-      <c r="B11" s="50" t="n">
-        <v>6794</v>
-      </c>
-      <c r="C11" s="79" t="n">
-        <v>0.008999999999999999</v>
+          <t>Direct or unknown</t>
+        </is>
+      </c>
+      <c r="B11" s="50" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C11" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="D11" s="50" t="n">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="E11" s="79" t="n">
-        <v>0.015</v>
+        <v>0.0175</v>
       </c>
       <c r="F11" s="48" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>0:06:15</t>
         </is>
       </c>
       <c r="G11" s="53" t="n">
-        <v>32</v>
+        <v>14.4068</v>
       </c>
       <c r="H11" s="79" t="n">
-        <v>0.133</v>
+        <v>0.0461</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="43">
       <c r="A12" s="71" t="inlineStr">
         <is>
-          <t>Direct or unknown</t>
+          <t>Other YouTube features</t>
         </is>
       </c>
       <c r="B12" s="48" t="inlineStr">
@@ -2476,27 +2302,27 @@
         </is>
       </c>
       <c r="D12" s="50" t="n">
-        <v>92</v>
+        <v>251</v>
       </c>
       <c r="E12" s="79" t="n">
-        <v>0.012</v>
+        <v>0.0318</v>
       </c>
       <c r="F12" s="48" t="inlineStr">
         <is>
-          <t>5:13</t>
+          <t>0:05:53</t>
         </is>
       </c>
       <c r="G12" s="53" t="n">
-        <v>8</v>
+        <v>16.744</v>
       </c>
       <c r="H12" s="79" t="n">
-        <v>0.033</v>
+        <v>0.0535</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="43">
       <c r="A13" s="71" t="inlineStr">
         <is>
-          <t>External</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B13" s="48" t="inlineStr">
@@ -2510,57 +2336,57 @@
         </is>
       </c>
       <c r="D13" s="50" t="n">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="E13" s="79" t="n">
-        <v>0.012</v>
+        <v>0.0025</v>
       </c>
       <c r="F13" s="48" t="inlineStr">
         <is>
-          <t>6:54</t>
+          <t>0:03:58</t>
         </is>
       </c>
       <c r="G13" s="53" t="n">
-        <v>9</v>
+        <v>1.1957</v>
       </c>
       <c r="H13" s="79" t="n">
-        <v>0.037</v>
+        <v>0.0038</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="43">
       <c r="A14" s="71" t="inlineStr">
         <is>
-          <t>Playlists</t>
+          <t>YouTube search</t>
         </is>
       </c>
       <c r="B14" s="50" t="n">
-        <v>1369</v>
+        <v>2741</v>
       </c>
       <c r="C14" s="79" t="n">
-        <v>0.027</v>
+        <v>0.0664</v>
       </c>
       <c r="D14" s="50" t="n">
-        <v>84</v>
+        <v>310</v>
       </c>
       <c r="E14" s="79" t="n">
-        <v>0.011</v>
+        <v>0.0393</v>
       </c>
       <c r="F14" s="48" t="inlineStr">
         <is>
-          <t>9:08</t>
+          <t>0:03:55</t>
         </is>
       </c>
       <c r="G14" s="53" t="n">
-        <v>11</v>
+        <v>15.7458</v>
       </c>
       <c r="H14" s="79" t="n">
-        <v>0.046</v>
+        <v>0.0504</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="43">
       <c r="A15" s="71" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Sound pages</t>
         </is>
       </c>
       <c r="B15" s="48" t="inlineStr">
@@ -2574,27 +2400,27 @@
         </is>
       </c>
       <c r="D15" s="50" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E15" s="79" t="n">
-        <v>0.002</v>
+        <v>0.0001</v>
       </c>
       <c r="F15" s="48" t="inlineStr">
         <is>
-          <t>5:02</t>
+          <t>0:00:40</t>
         </is>
       </c>
       <c r="G15" s="53" t="n">
-        <v>1.2</v>
+        <v>0.0113</v>
       </c>
       <c r="H15" s="79" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="43">
       <c r="A16" s="71" t="inlineStr">
         <is>
-          <t>Related Shorts</t>
+          <t>Shorts feed</t>
         </is>
       </c>
       <c r="B16" s="48" t="inlineStr">
@@ -2608,27 +2434,27 @@
         </is>
       </c>
       <c r="D16" s="50" t="n">
-        <v>15</v>
+        <v>5952</v>
       </c>
       <c r="E16" s="79" t="n">
-        <v>0.002</v>
+        <v>0.7546</v>
       </c>
       <c r="F16" s="48" t="inlineStr">
         <is>
-          <t>0:04</t>
+          <t>0:00:35</t>
         </is>
       </c>
       <c r="G16" s="53" t="n">
-        <v>0</v>
+        <v>22.6648</v>
       </c>
       <c r="H16" s="79" t="n">
-        <v>0</v>
+        <v>0.0725</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="43">
       <c r="A17" s="71" t="inlineStr">
         <is>
-          <t>Sound pages</t>
+          <t>Related Shorts</t>
         </is>
       </c>
       <c r="B17" s="48" t="inlineStr">
@@ -2642,21 +2468,21 @@
         </is>
       </c>
       <c r="D17" s="50" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E17" s="79" t="n">
-        <v>0</v>
+        <v>0.0019</v>
       </c>
       <c r="F17" s="48" t="inlineStr">
         <is>
-          <t>0:40</t>
+          <t>0:00:04</t>
         </is>
       </c>
       <c r="G17" s="53" t="n">
-        <v>0</v>
+        <v>0.0199</v>
       </c>
       <c r="H17" s="79" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
     </row>
   </sheetData>
